--- a/_ForDRA/BVSimulationFiles/86.xlsx
+++ b/_ForDRA/BVSimulationFiles/86.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0006784565916398713</v>
+        <v>0.01356913183279743</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0006909798612286343</v>
+        <v>0.01381959722457269</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007035031308173972</v>
+        <v>0.01407006261634794</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007160264004061601</v>
+        <v>0.0143205280081232</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007285496699949229</v>
+        <v>0.01457099339989846</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007410729395836859</v>
+        <v>0.01482145879167372</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007535962091724486</v>
+        <v>0.01507192418344897</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007661194787612117</v>
+        <v>0.01532238957522423</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007786427483499746</v>
+        <v>0.01557285496699949</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007911660179387376</v>
+        <v>0.01582332035877475</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008036892875275005</v>
+        <v>0.01607378575055001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008162125571162634</v>
+        <v>0.01632425114232527</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008287358267050263</v>
+        <v>0.01657471653410053</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000841259096293789</v>
+        <v>0.01682518192587578</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008537823658825522</v>
+        <v>0.01707564731765104</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.000866305635471315</v>
+        <v>0.0173261127094263</v>
       </c>
       <c r="R2" t="n">
-        <v>0.000878828905060078</v>
+        <v>0.01757657810120156</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008913521746488407</v>
+        <v>0.01782704349297681</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0009038754442376038</v>
+        <v>0.01807750888475208</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009163987138263665</v>
+        <v>0.01832797427652733</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0006784565916398713</v>
+        <v>0.01356913183279743</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0006909798612286343</v>
+        <v>0.01381959722457269</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007035031308173972</v>
+        <v>0.01407006261634794</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007160264004061601</v>
+        <v>0.0143205280081232</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007285496699949229</v>
+        <v>0.01457099339989846</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007410729395836859</v>
+        <v>0.01482145879167372</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007535962091724486</v>
+        <v>0.01507192418344897</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007661194787612117</v>
+        <v>0.01532238957522423</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007786427483499746</v>
+        <v>0.01557285496699949</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007911660179387376</v>
+        <v>0.01582332035877475</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008036892875275005</v>
+        <v>0.01607378575055001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0008162125571162634</v>
+        <v>0.01632425114232527</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008287358267050263</v>
+        <v>0.01657471653410053</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000841259096293789</v>
+        <v>0.01682518192587578</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008537823658825522</v>
+        <v>0.01707564731765104</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000866305635471315</v>
+        <v>0.0173261127094263</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000878828905060078</v>
+        <v>0.01757657810120156</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008913521746488407</v>
+        <v>0.01782704349297681</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0009038754442376038</v>
+        <v>0.01807750888475208</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0009163987138263665</v>
+        <v>0.01832797427652733</v>
       </c>
     </row>
   </sheetData>
